--- a/users.xlsx
+++ b/users.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,57 @@
         </is>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mr. Sharma</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t123</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ms. Roy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t123</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dr. Sen</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t123</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>teacher</t>
         </is>
